--- a/tests/fixtures/test_connections.xlsx
+++ b/tests/fixtures/test_connections.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HiddenData" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalBudget">'[budget.xlsx]Summary'!$A$1:$Z$100</definedName>
@@ -199,6 +200,19 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6140000-1111-2222-3333-44445555AAAB}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Summary"/>
+    </sheetNames>
+    <definedNames/>
+    <sheetDataSet/>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,6 +575,12 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <f>BDP("AAPL US Equity","PX_LAST")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
@@ -596,4 +616,95 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Discount Rate</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Source: Bloomberg as of 12/31/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Per FactSet consensus estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Source: Company filings 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shares Outstanding (MM)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1234.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Data from Reuters</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>